--- a/input/DatabaseCountryYear.xlsx
+++ b/input/DatabaseCountryYear.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="9">
   <si>
     <t>Country</t>
   </si>
@@ -99,7 +99,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
